--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_214_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_214_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4778</v>
+        <v>3.7076</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0986</v>
+        <v>2.8326</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3792</v>
+        <v>0.8751</v>
       </c>
       <c r="G2" t="n">
         <v>3.2993</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8796</v>
+        <v>1.1095</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>0.5939</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0196</v>
+        <v>0.5155</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8608</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0135</v>
+        <v>3.1388</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2533</v>
+        <v>3.8745</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2398</v>
+        <v>-0.7357</v>
       </c>
       <c r="G3" t="n">
         <v>0.8986</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6531</v>
+        <v>-0.5278</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.326</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7059</v>
+        <v>-0.2018</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3076</v>
+        <v>0.8108</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1797</v>
+        <v>0.6829</v>
       </c>
       <c r="F4" t="n">
         <v>0.1279</v>
@@ -766,10 +766,10 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3383</v>
+        <v>0.165</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5737</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>0.2355</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0751</v>
+        <v>-0.025</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2312</v>
+        <v>-0.3491</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1561</v>
+        <v>0.3241</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2697</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0373</v>
+        <v>0.0127</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3009</v>
+        <v>-0.1329</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2692</v>
+        <v>-0.243</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0623</v>
+        <v>-0.9226</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3315</v>
+        <v>0.6795</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5789</v>
+        <v>0.128</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3313</v>
+        <v>1.4896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2476</v>
+        <v>-1.3617</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2117</v>
+        <v>0.4028</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8571</v>
+        <v>0.9683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3546</v>
+        <v>-0.5655</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6327</v>
+        <v>-0.2749</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.5213</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.107</v>
+        <v>-0.7961</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.224</v>
+        <v>-0.1417</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.2199</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3734</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7463</v>
+        <v>-0.2692</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4258</v>
+        <v>1.0623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6795</v>
+        <v>-1.3315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.128</v>
+        <v>0.5789</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4896</v>
+        <v>0.3313</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3617</v>
+        <v>0.2476</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4028</v>
+        <v>1.2117</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9683</v>
+        <v>0.8571</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5655</v>
+        <v>0.3546</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2749</v>
+        <v>-0.6327</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5213</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7961</v>
+        <v>-0.107</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6449</v>
+        <v>0.224</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7231</v>
+        <v>-0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.3734</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9004</v>
+        <v>-1.9676</v>
       </c>
       <c r="E8" t="n">
         <v>0.2839</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1842</v>
+        <v>-2.2515</v>
       </c>
       <c r="G8" t="n">
         <v>-0.866</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1942</v>
+        <v>-0.2614</v>
       </c>
       <c r="T8" t="n">
         <v>0.2636</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4577</v>
+        <v>-0.525</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4414</v>
+        <v>-1.9981</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9111</v>
+        <v>-1.2408</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5303</v>
+        <v>-0.7573</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3803</v>
+        <v>3.2324</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3757</v>
+        <v>-0.1671</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7561</v>
+        <v>3.3995</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1494</v>
+        <v>2.7604</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1126</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>3.6168</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5298</v>
+        <v>0.472</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7369</v>
+        <v>0.6893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7929</v>
+        <v>-0.2173</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-4.639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-5.7988</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9801</v>
+        <v>0.3389</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6765</v>
+        <v>0.0474</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3036</v>
+        <v>0.2915</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1134</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.5773</v>
+        <v>1.7501</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6529</v>
+        <v>-2.9111</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.862</v>
+        <v>-1.6647</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7909</v>
+        <v>-1.2465</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2324</v>
+        <v>-2.4268</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1671</v>
+        <v>-0.8609</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3995</v>
+        <v>-1.5659</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7604</v>
+        <v>-1.4439</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.4601</v>
       </c>
       <c r="L10" t="n">
-        <v>3.6168</v>
+        <v>-0.9838</v>
       </c>
       <c r="M10" t="n">
-        <v>0.472</v>
+        <v>-0.9829</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6893</v>
+        <v>-0.4008</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2173</v>
+        <v>-0.5821</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3159</v>
+        <v>-0.7705</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5737</v>
+        <v>-0.275</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2579</v>
+        <v>-0.4955</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9304</v>
+        <v>1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7501</v>
+        <v>1.214</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6518</v>
+        <v>-3.4009</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1365</v>
+        <v>-1.5008</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5153</v>
+        <v>-1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4268</v>
+        <v>-0.3803</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8609</v>
+        <v>0.3757</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5659</v>
+        <v>-0.7561</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4439</v>
+        <v>1.1494</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4601</v>
+        <v>1.1126</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9838</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9829</v>
+        <v>-1.5298</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4008</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5821</v>
+        <v>-0.7929</v>
       </c>
       <c r="P11" t="n">
         <v>-0.9278</v>
@@ -1312,22 +1312,22 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5112</v>
+        <v>0.0206</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>0.0868</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7644</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.214</v>
+        <v>-2.1134</v>
       </c>
       <c r="W11" t="n">
-        <v>1.214</v>
+        <v>-1.5773</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6045</v>
+        <v>-4.6381</v>
       </c>
       <c r="E12" t="n">
         <v>-3.4128</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1917</v>
+        <v>-1.2253</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4224</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2544</v>
+        <v>-0.288</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2192</v>
+        <v>-0.2528</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.5427</v>
+        <v>-7.7958</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.101599999999999</v>
+        <v>-0.3545999999999996</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.441</v>
+        <v>-7.441199999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.490100000000001</v>
+        <v>2.4901</v>
       </c>
       <c r="H13" t="n">
         <v>6.721900000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.231999999999999</v>
+        <v>-4.232</v>
       </c>
       <c r="J13" t="n">
         <v>8.7788</v>
@@ -1447,7 +1447,7 @@
         <v>5.3331</v>
       </c>
       <c r="L13" t="n">
-        <v>3.445600000000001</v>
+        <v>3.4456</v>
       </c>
       <c r="M13" t="n">
         <v>-6.288799999999999</v>
@@ -1456,40 +1456,40 @@
         <v>1.3886</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.677499999999999</v>
+        <v>-7.6775</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.7986</v>
+        <v>-5.798599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7575</v>
       </c>
       <c r="R13" t="n">
-        <v>6.959</v>
+        <v>6.959000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8656000000000001</v>
+        <v>-0.1187000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6852</v>
+        <v>0.06139999999999993</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1798999999999999</v>
+        <v>-0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.368499999999999</v>
+        <v>-4.3685</v>
       </c>
       <c r="W13" t="n">
         <v>3.5623</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.9308</v>
+        <v>-7.930800000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.67</v>
+        <v>4.5816</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5626</v>
+        <v>3.7578</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1074</v>
+        <v>0.8238</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1891</v>
+        <v>0.3991</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6386</v>
+        <v>-1.0362</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8277</v>
+        <v>1.4353</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0068</v>
+        <v>1.5433</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.5068</v>
+        <v>-0.6849</v>
       </c>
       <c r="L14" t="n">
-        <v>4.5136</v>
+        <v>2.2281</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1823</v>
+        <v>-1.1442</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8681</v>
+        <v>-0.3513</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6859</v>
+        <v>-0.7929</v>
       </c>
       <c r="P14" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4424</v>
+        <v>0.6438</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5558</v>
+        <v>0.1577</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8865</v>
+        <v>0.4861</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4254</v>
+        <v>3.0748</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4254</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7502</v>
+        <v>3.8906</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0501</v>
+        <v>3.0292</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3991</v>
+        <v>2.1891</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0362</v>
+        <v>-1.6386</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4353</v>
+        <v>3.8277</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5433</v>
+        <v>2.0068</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6849</v>
+        <v>-2.5068</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2281</v>
+        <v>4.5136</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1442</v>
+        <v>0.1823</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3513</v>
+        <v>0.8681</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7929</v>
+        <v>-0.6859</v>
       </c>
       <c r="P15" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1876</v>
+        <v>1.663</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.55</v>
+        <v>1.0225</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3624</v>
+        <v>0.6405</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0748</v>
+        <v>-0.4254</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0347</v>
+        <v>2.8945</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6214</v>
+        <v>1.1339</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4133</v>
+        <v>1.7606</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0596</v>
+        <v>0.9534</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3903</v>
+        <v>-0.4284</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6693</v>
+        <v>1.3818</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2565</v>
+        <v>1.5474</v>
       </c>
       <c r="K16" t="n">
         <v>0.3732</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8833</v>
+        <v>1.1742</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1969</v>
+        <v>-0.5941</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0171</v>
+        <v>-0.8016</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.214</v>
+        <v>0.2075</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8307</v>
+        <v>0.405</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6844</v>
+        <v>-0.094</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1463</v>
+        <v>0.4991</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0275</v>
+        <v>2.425</v>
       </c>
       <c r="E17" t="n">
-        <v>3.371</v>
+        <v>3.0171</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3435</v>
+        <v>-0.5921</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9298999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4213</v>
+        <v>0.8189</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0227</v>
+        <v>0.6688</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6014</v>
+        <v>0.15</v>
       </c>
       <c r="V17" t="n">
         <v>1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2102</v>
+        <v>2.0404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1903</v>
+        <v>1.5035</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0199</v>
+        <v>0.5369</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9534</v>
+        <v>1.0596</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4284</v>
+        <v>0.3903</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3818</v>
+        <v>0.6693</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5474</v>
+        <v>1.2565</v>
       </c>
       <c r="K18" t="n">
         <v>0.3732</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1742</v>
+        <v>0.8833</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5941</v>
+        <v>-0.1969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8016</v>
+        <v>0.0171</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2075</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2792</v>
+        <v>0.8364</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0376</v>
+        <v>0.5665</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2416</v>
+        <v>0.27</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0977</v>
+        <v>1.2886</v>
       </c>
       <c r="E19" t="n">
         <v>0.327</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7708</v>
+        <v>0.9617</v>
       </c>
       <c r="G19" t="n">
         <v>0.2788</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4336</v>
+        <v>-0.2427</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1349</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
         <v>0.7886</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0897</v>
+        <v>0.7746</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7076</v>
+        <v>-0.4717</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7974</v>
+        <v>1.2463</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4151</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9796</v>
+        <v>-0.2948</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3075</v>
+        <v>0.1415</v>
       </c>
       <c r="V20" t="n">
         <v>0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0492</v>
+        <v>-0.2919</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.359</v>
+        <v>-1.477</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4082</v>
+        <v>1.185</v>
       </c>
       <c r="G21" t="n">
         <v>-1.566</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5456</v>
+        <v>0.2045</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3339</v>
+        <v>-0.4518</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7271</v>
+        <v>-0.7441</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1354</v>
+        <v>-0.3097</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5917</v>
+        <v>-0.4344</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0233</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3996</v>
+        <v>-0.4167</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4189</v>
+        <v>-0.5933</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0193</v>
+        <v>0.1766</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6595</v>
+        <v>-5.9576</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4793</v>
+        <v>-3.0691</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1802</v>
+        <v>-2.8885</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4356</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0949</v>
+        <v>-0.393</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2284</v>
+        <v>-0.3613</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3233</v>
+        <v>-0.0316</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7527</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.542599999999997</v>
+        <v>10.9017</v>
       </c>
       <c r="E24" t="n">
-        <v>7.441099999999999</v>
+        <v>7.440999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.101699999999999</v>
+        <v>3.4607</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4899</v>
@@ -2299,13 +2299,13 @@
         <v>4.232099999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>6.288600000000001</v>
+        <v>6.288600000000002</v>
       </c>
       <c r="K24" t="n">
         <v>-1.3887</v>
       </c>
       <c r="L24" t="n">
-        <v>7.6776</v>
+        <v>7.677599999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-8.778799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.7574</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8655000000000004</v>
+        <v>3.224399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1801</v>
+        <v>0.1802</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6853</v>
+        <v>3.0445</v>
       </c>
       <c r="V24" t="n">
         <v>4.3684</v>
